--- a/data/attendance_records.xlsx
+++ b/data/attendance_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,33 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>hazemmahmoud3038@gmail.com</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>8bdb0685-5efb-4453-82e3-8b8bd6fdc20e</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Attended</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-05 12:11:52</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>C:\Users\user\Downloads\bioinfo_prog\attendance_app\qr_codes\qr_8bdb0685-5efb-4453-82e3-8b8bd6fdc20e.png</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
